--- a/data-validation/マスタ誤り疑いリスト.xlsx
+++ b/data-validation/マスタ誤り疑いリスト.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -515,172 +515,172 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>422</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>フィリペンデュラ　ウルマリア ‘バリエガータ’</t>
+          <t>カレックス‘バッドヘアーデイズ’</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Filipendula ulmaria 'Variegata'</t>
+          <t>Carex ‛Bad Hair Days’</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ヨーロッパ、西アジア</t>
+          <t>北米</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>耐潮性_根拠</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>JSONの記述通りMangave属の園芸品種。多肉植物アガベの近縁であり、ナーサリーサイトで中程度の耐潮性があると記載。乾燥に強く排水を要す</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>耐潮性根拠に別分類群/多肉の記述が混入の疑い</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>カレックス ディバルサ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Carex divulsa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ヨーロッパ、北アフリカ、コーカサス地域、中央アジア</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>耐暑性に関する注記</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>湿地・草原原産で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>注記は高温多湿に強いと断定だが耐暑性(検証済)=弱と矛盾</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>フィリペンデュラ　ウルマリア</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Filipendula ulmaria</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、西アジア</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>カレックス フラジェリフェア ‘キウイ’</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Carex flagellifera 'Kiwi'</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ニュージーランド、タスマニア、チャタム諸島</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>耐暑性に関する注記</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>湿地・草原原産で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>注記は高温多湿に強いと断定だが耐暑性(検証済)=弱と矛盾</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ネペタ　サブセッシリス ‘ブルードリーム’</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nepeta subsessilis 'Blue Dreams'</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>日本</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ユーパトリウム　白花</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Eupatorium album L.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>北米東部</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>耐暑性に関する注記</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MBGで「Somewhat intolerant of the heat and humidity of the deep South」と記</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>注記は乾燥好きだが乾燥耐性(検証済)=弱と矛盾</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>コレオプシス　ロゼア ‘アメリカンドリーム’</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Coreopsis rosea 'American Dream'</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MBGで「Tolerant of heat, humidity and drought」と記載。北米プレーリー原産で高温多湿耐性あり。日本で</t>
+          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of h</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>注記は高温多湿に強いと断定だが耐暑性(検証済)=弱と矛盾</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -688,29 +688,29 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>カンパニュラ　プンクタータ ‘ホットリップス’</t>
+          <t>アルメリア　マリティマ ‘バリエガータ’（アルメリア斑入り）</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Campanula punctata 'Hot Lips'</t>
+          <t>Armeria maritima 'Variegata'</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Siberia, Japan</t>
+          <t>ヨーロッパ、北米</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -720,42 +720,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>日本・東アジア原産で高温多湿耐性あり。日本の夏越し安定。</t>
+          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>注記は高温多湿に強いと断定だが耐暑性(検証済)=弱と矛盾</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>フェスツーカ　グラウカ ‘エリジャーブルー’</t>
+          <t>アルメリア　マリティマ ‘ルブリフォーリア’</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Festuca glauca ‛Elijah Blue’</t>
+          <t>Armeria maritima 'Rubrifolia'</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ヨーロッパ</t>
+          <t>ヨーロッパ、北米</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>乾燥地原産のイネ科植物。高湿度環境では蒸れに弱い。水はけと通風が必須。</t>
+          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -778,29 +778,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>フェスツーカ　グラウカ ‘ボルダーブルー’</t>
+          <t>アルメリア　マリティマ‘アルバ’ （アルメリア白花）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Festuca glauca 'Boulder Blue'</t>
+          <t>Armeria maritima 'Alba'</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>中央ヨーロッパ、南ヨーロッパ</t>
+          <t>ヨーロッパ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -810,12 +810,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>乾燥地原産のイネ科植物。高湿度環境では蒸れに弱い。水はけと通風が必須。</t>
+          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -823,29 +823,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>フェスツーカ　アイダホエンシス</t>
+          <t>アルメリア　マリティマ （アルメリア　ピンク）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Festuca idahoensis</t>
+          <t>Armeria maritima</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>北米西部</t>
+          <t>ヨーロッパ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>乾燥地原産のイネ科植物。高湿度環境では蒸れに弱い。水はけと通風が必須。</t>
+          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -868,29 +868,29 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>フェスツーカ スコパリア（ホビット）</t>
+          <t>ガリウム　ベラム（カワラマツバ）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Festuca gautieri</t>
+          <t>Galium verum</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ピレネー山脈、南西ヨーロッパ</t>
+          <t>ヨーロッパ、南西アジア</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,42 +900,42 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>乾燥地原産のイネ科植物。高湿度環境では蒸れに弱い。水はけと通風が必須。</t>
+          <t>ヨーロッパ・アジアの森林下草。半日陰・湿潤環境を好む。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ユーホルビア　ポリクロマ</t>
+          <t>ヤブラン白斑シルバードラゴン</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Euphorbia polychroma</t>
+          <t>Liriope spicata 'Gin-ryū' (SILVER DRAGON)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中央および南東ヨーロッパ、アジアマイナー</t>
+          <t>日本・中国</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -945,42 +945,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>乾燥地原産の多肉質植物。高湿度環境では根腐れしやすい。水はけと通風が必須。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>ヤブラン（Liriope muscari）：日本・東アジア原産の常緑多年草。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ユーホルビア‘クラリスハワード’</t>
+          <t>ファラリス （フイリクサヨシ・アシフイリ）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Euphorbia cyparissias 'Clarice Howard'</t>
+          <t>Phalaris arundinacea var. picta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ヨーロッパ</t>
+          <t>ヨーロッパ・北アジア・北米</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -990,42 +990,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>乾燥地原産の多肉質植物。高湿度環境では根腐れしやすい。水はけと通風が必須。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>ファラリス（Phalaris arundinacea）：湿地・川辺原産のイネ科植物。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ユーホルビア　アミグダロイデス ‘ゴールデングローリー’</t>
+          <t>カレックス‘アイスファウンテン’</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Euphorbia amygdaloides 'Golden Glory'</t>
+          <t>Carex muskingumensis ‘Ice Fountains’</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ヨーロッパ、トルコ、コーカサス</t>
+          <t>北米東部および中央部</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1035,42 +1035,42 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>乾燥地原産の多肉質植物。高湿度環境では根腐れしやすい。水はけと通風が必須。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>817</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>アルテミシア　シュミッディアーナ ‘ナナ’（アサギリソウ）</t>
+          <t>カレックス　マスキングメンシス ‘リトルミッジ’</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Artemisia schmidtiana 'Nana'</t>
+          <t>Carex muskingumensis 'Little Midge'</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>北米東部</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1080,42 +1080,42 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>銀葉・毛の多い葉を持つ乾燥地原産植物。高湿度環境では蒸れによる葉腐れ・株腐れが発生しやすい。水はけと通風が必須。</t>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>855</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>アルテミシア ブルガリス ‘オリエンタルライムライト’ （フイリヨモギ）</t>
+          <t>トロリウス　チネンシス ‘ゴールデンクィーン’</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Artemisia vulgaris 'Janlim'</t>
+          <t>Trollius chinensis 'Golden Queen'</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ヨーロッパ、北アジア（ロシアから日本、韓国まで）</t>
+          <t>南シベリア、ロシア極東南部、中国北部</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1125,57 +1125,57 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>銀葉・毛の多い葉を持つ乾燥地原産植物。高湿度環境では蒸れによる葉腐れ・株腐れが発生しやすい。水はけと通風が必須。</t>
+          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>非多肉属に「多肉/乾燥地原産」注記（属の生態不一致）</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>カレックス‘バッドヘアーデイズ’</t>
+          <t>フィソカルパス‘ディアボロ’ （アメリカテマリシモツケ ディアボロ）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Carex ‛Bad Hair Days’</t>
+          <t>Physocarpus opulifolius ‛Diabolo’</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>北米</t>
+          <t>北米東部</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>耐潮性_根拠</t>
+          <t>耐暑性に関する注記</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JSONの記述通りMangave属の園芸品種。多肉植物アガベの近縁であり、ナーサリーサイトで中程度の耐潮性があると記載。乾燥に強く排水を要す</t>
+          <t>MBGで「hot, humid summers」には午後の日陰を推奨。Gardenia.netで「doesn't enjoy hot and</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>耐潮性根拠に別分類群/多肉の記述が混入の疑い</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1183,29 +1183,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>832</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>サリクトラム（タリクトラム） ロチブルニエナム</t>
+          <t>ユーパトリム　ルゴサム ‘チョコレート’</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Thalictrum rochebrunianum</t>
+          <t>Ageratina altissima 'Chocolate'</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>東アジア</t>
+          <t>北米東部</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>日本原産で比較的高温多湿耐性あり。MBGで「May grow poorly in climates with hot, humid summ</t>
+          <t>北米東部原産。比較的高温多湿に適応するが、半日陰・適湿管理が必要。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>注記は高温多湿に強いと断定だが耐暑性(検証済)=弱と矛盾</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1228,29 +1228,29 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>876</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>カレックス ディバルサ</t>
+          <t>ヤナギラン</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Carex divulsa</t>
+          <t>Chamerion angustifolium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ヨーロッパ、北アフリカ、コーカサス地域、中央アジア</t>
+          <t>北半球温帯全般 (ヨーロッパ、アジア、北アメリカ)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1260,690 +1260,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>北半球冷涼地原産。MBGで「Prefers part shade in hot summer climates」と明記。半日陰・適湿管理で夏</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1892</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>カレックス フラジェリフェア ‘キウイ’</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Carex flagellifera 'Kiwi'</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ニュージーランド、タスマニア、チャタム諸島</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ユーパトリウム　白花</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Eupatorium album L.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of h</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ ‘バリエガータ’（アルメリア斑入り）</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Armeria maritima 'Variegata'</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、北米</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ ‘ルブリフォーリア’</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Armeria maritima 'Rubrifolia'</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、北米</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ‘アルバ’ （アルメリア白花）</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Armeria maritima 'Alba'</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ヨーロッパ</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ （アルメリア　ピンク）</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Armeria maritima</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ヨーロッパ</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1480</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ガリウム　ベラム（カワラマツバ）</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Galium verum</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、南西アジア</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ヨーロッパ・アジアの森林下草。半日陰・湿潤環境を好む。通風確保で夏越し可能。</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ヤブラン白斑シルバードラゴン</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Liriope spicata 'Gin-ryū' (SILVER DRAGON)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>日本・中国</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ヤブラン（Liriope muscari）：日本・東アジア原産の常緑多年草。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ファラリス （フイリクサヨシ・アシフイリ）</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Phalaris arundinacea var. picta</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ヨーロッパ・北アジア・北米</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ファラリス（Phalaris arundinacea）：湿地・川辺原産のイネ科植物。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>カレックス‘アイスファウンテン’</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Carex muskingumensis ‘Ice Fountains’</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>北米東部および中央部</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>カレックス　マスキングメンシス ‘リトルミッジ’</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Carex muskingumensis 'Little Midge'</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>トロリウス　チネンシス ‘ゴールデンクィーン’</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Trollius chinensis 'Golden Queen'</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>南シベリア、ロシア極東南部、中国北部</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>フィソカルパス‘ディアボロ’ （アメリカテマリシモツケ ディアボロ）</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Physocarpus opulifolius ‛Diabolo’</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>MBGで「hot, humid summers」には午後の日陰を推奨。Gardenia.netで「doesn't enjoy hot and</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ユーパトリム　ルゴサム ‘チョコレート’</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Ageratina altissima 'Chocolate'</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>北米東部原産。比較的高温多湿に適応するが、半日陰・適湿管理が必要。</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ヤナギラン</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Chamerion angustifolium</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>北半球温帯全般 (ヨーロッパ、アジア、北アメリカ)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>北半球冷涼地原産。MBGで「Prefers part shade in hot summer climates」と明記。半日陰・適湿管理で夏</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1958,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -2023,28 +1348,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>湿地・草原原産で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>北米東部原産で高温多湿耐性あり。MBGで「tolerates heat and humidity」と記載。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>北米東部原産で高温多湿耐性あり。MBGで「tolerates heat and humidity」と記載。日本でも夏越し安定。</t>
+          <t>湿地・草原原産で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2241,33 +1566,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MBGで「Somewhat intolerant of the heat and humidity of the deep South」と記載。地中海・中央アジア原産で乾燥を好む。通風確保・水はけが良ければ夏越し可能。</t>
+          <t>ヨーロッパの森林下草。半日陰・湿潤環境を好む。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ヨーロッパの森林下草。半日陰・湿潤環境を好む。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
+          <t>ヨーロッパ・アジア原産。通風・水はけが良ければ夏越し可能。高湿度では根腐れリスクあり。</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>10</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ヨーロッパ・アジア原産。通風・水はけが良ければ夏越し可能。高湿度では根腐れリスクあり。</t>
+          <t>地中海・ヨーロッパ原産。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -2278,18 +1603,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>地中海・ヨーロッパ原産。高湿度環境では根腐れしやすい。</t>
+          <t>ヨーロッパ・アジア原産。冷涼環境を好む。通風・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ヨーロッパ・アジア原産。冷涼環境を好む。通風・水はけが良ければ夏越し可能。</t>
+          <t>MBGで「Somewhat intolerant of the heat and humidity of the deep South」と記載。地中海・中央アジア原産で乾燥を好む。通風確保・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -2403,18 +1728,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>日本・東アジア原産で高温多湿耐性あり。日本の夏越し安定。</t>
+          <t>中央アジア・地中海原産の乾燥地植物。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>6</v>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MBGで「Tolerant of heat, humidity and drought」と記載。北米プレーリー原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>北米東部原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2425,33 +1754,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>中央アジア・地中海原産の乾燥地植物。高湿度環境では根腐れしやすい。</t>
+          <t>地中海・南米原産。水はけの良い土壌と通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>6</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>北米東部原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>ヨーロッパ山地原産。冷涼・湿潤環境を好む。日本の高温多湿では半日陰・通風確保が必要。</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>6</v>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>地中海・南米原産。水はけの良い土壌と通風確保で夏越し可能。</t>
+          <t>MBGで「Plants need good air circulation」と記載。北米東部原産だが、高湿度環境ではうどんこ病が発生しやすい。通風確保が必須。耐病性品種を選ぶと夏越し安定。</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2462,22 +1791,18 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ヨーロッパ山地原産。冷涼・湿潤環境を好む。日本の高温多湿では半日陰・通風確保が必要。</t>
+          <t>北米南部原産で高温多湿耐性あり。MBGで「tolerates heat and humidity」と記載。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>6</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MBGで「Plants need good air circulation」と記載。北米東部原産だが、高湿度環境ではうどんこ病が発生しやすい。通風確保が必須。耐病性品種を選ぶと夏越し安定。</t>
+          <t>Plant Delightsで「dislike waterlogged soils and hot, humid summers」と記載。地中海・中央アジア原産で乾燥を好む。通風確保・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2488,7 +1813,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>北米南部原産で高温多湿耐性あり。MBGで「tolerates heat and humidity」と記載。日本でも夏越し安定。</t>
+          <t>MBGで「tolerates heat and humidity」と記載。北米プレーリー原産で高温多湿耐性あり。</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2499,7 +1824,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Plant Delightsで「dislike waterlogged soils and hot, humid summers」と記載。地中海・中央アジア原産で乾燥を好む。通風確保・水はけが良ければ夏越し可能。</t>
+          <t>MBGで「tolerate hot, humid summers」と記載。通風と水はけを確保すれば夏越し可能。</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2510,59 +1835,59 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBGで「tolerates heat and humidity」と記載。北米プレーリー原産で高温多湿耐性あり。</t>
+          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of heat and humidity」と記載。北米湿地・草原原産で高温多湿耐性あり。</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>6</v>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MBGで「tolerate hot, humid summers」と記載。通風と水はけを確保すれば夏越し可能。</t>
+          <t>MBGで高温多湿環境での株腐れ（crown rot）リスクを記載。通風確保と水はけが必要。半日陰で管理すると夏越し安定。</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
-      </c>
-      <c r="C47" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of heat and humidity」と記載。北米湿地・草原原産で高温多湿耐性あり。</t>
+          <t>東アジア原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>6</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MBGで高温多湿環境での株腐れ（crown rot）リスクを記載。通風確保と水はけが必要。半日陰で管理すると夏越し安定。</t>
+          <t>日本・東アジア原産で高温多湿耐性あり。日本の夏越し安定。</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>5</v>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>東アジア原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>MBGで「Tolerant of heat, humidity and drought」と記載。北米プレーリー原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2780,85 +2105,85 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>乾燥地原産のイネ科植物。高湿度環境では蒸れに弱い。水はけと通風が必須。</t>
+          <t>通風・水はけが良ければ夏越し可能。うどんこ病に注意。</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>4</v>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>通風・水はけが良ければ夏越し可能。うどんこ病に注意。</t>
+          <t>地中海原産の乾燥地植物。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>地中海原産の乾燥地植物。高湿度環境では根腐れしやすい。</t>
+          <t>MBGで「tolerates hot, humid summers」と記載。北米プレーリー原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MBGで「tolerates hot, humid summers」と記載。北米プレーリー原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>高山植物。冷涼・湿潤環境を好む。日本の高温多湿では夏越しが困難。</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>4</v>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>高山植物。冷涼・湿潤環境を好む。日本の高温多湿では夏越しが困難。</t>
+          <t>南アフリカ原産。通風・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>4</v>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>南アフリカ原産。通風・水はけが良ければ夏越し可能。</t>
+          <t>湿潤環境に適応するが、過湿での根腐れリスクあり。半日陰・水はけの良い土壌で夏越し可能。</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>4</v>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>湿潤環境に適応するが、過湿での根腐れリスクあり。半日陰・水はけの良い土壌で夏越し可能。</t>
+          <t>ヨーロッパ高山植物。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2873,22 +2198,18 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ヨーロッパ高山植物。高湿度環境では根腐れしやすい。</t>
+          <t>東アジア原産の交配種。高温多湿に適応し、日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>4</v>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>東アジア原産の交配種。高温多湿に適応し、日本でも夏越し安定。</t>
+          <t>ヨーロッパ原産の交配種。高温多湿には弱く、水はけと通風確保が必要。</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2899,33 +2220,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ヨーロッパ原産の交配種。高温多湿には弱く、水はけと通風確保が必要。</t>
+          <t>MBGで暑い夏の気候では直射日光・乾燥により葉が焼ける可能性を記載。半日陰で管理し土壌の乾燥に注意。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
-      </c>
-      <c r="C77" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MBGで暑い夏の気候では直射日光・乾燥により葉が焼ける可能性を記載。半日陰で管理し土壌の乾燥に注意。通風確保で夏越し可能。</t>
+          <t>地中海原産で乾燥を好む。高湿度環境では根腐れしやすい。水はけと通風が必須。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>3</v>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>地中海原産で乾燥を好む。高湿度環境では根腐れしやすい。水はけと通風が必須。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>韓国・日本原産で高温多湿耐性あり。日本の夏越し安定。MBGで「tolerates heat and humidity」と記載。</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2936,33 +2257,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>韓国・日本原産で高温多湿耐性あり。日本の夏越し安定。MBGで「tolerates heat and humidity」と記載。</t>
+          <t>北米・東アジアの森林下草。半日陰・湿潤環境を好む。日本の高温多湿では半日陰管理が必要。</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>3</v>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>北米・東アジアの森林下草。半日陰・湿潤環境を好む。日本の高温多湿では半日陰管理が必要。</t>
+          <t>MBGで「woolly leaves trap moisture, and in humid climates such as the St. Louis area, plant leaves are susceptible to attack from rot and fungal diseases」と記載。毛の多い葉が湿気を閉じ込め蒸れに弱い。日本の梅雨〜夏は株腐れが発生しやすい。</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>3</v>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MBGで「woolly leaves trap moisture, and in humid climates such as the St. Louis area, plant leaves are susceptible to attack from rot and fungal diseases」と記載。毛の多い葉が湿気を閉じ込め蒸れに弱い。日本の梅雨〜夏は株腐れが発生しやすい。</t>
+          <t>北米原産。通風・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2973,33 +2294,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>北米原産。通風・水はけが良ければ夏越し可能。</t>
+          <t>日本・東アジア原産の森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>3</v>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>日本・東アジア原産の森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>北米南部原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>3</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>乾燥地原産の多肉質植物。高湿度環境では根腐れしやすい。水はけと通風が必須。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>東アジア原産だが乾燥地を好む。高湿度環境では根腐れしやすい。水はけと通風が必須。</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3014,59 +2335,59 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>北米南部原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>東アジア・日本原産の湿地植物。高湿度環境に適応。</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>3</v>
       </c>
-      <c r="C86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>東アジア原産だが乾燥地を好む。高湿度環境では根腐れしやすい。水はけと通風が必須。</t>
+          <t>Chicago Botanic Gardenで比較的高温多湿耐性ありと記載。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>3</v>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>東アジア・日本原産の湿地植物。高湿度環境に適応。</t>
+          <t>MBGで「tolerates heat and humidity」と記載。北米東部原産のプレーリー植物で高温多湿耐性あり。</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>3</v>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Chicago Botanic Gardenで比較的高温多湿耐性ありと記載。通風確保で夏越し可能。</t>
+          <t>冷涼地原産。日本の高温多湿では夏越しが困難。梅雨〜夏は株が傷みやすい。高温多湿での葉枯れ・株腐れが発生しやすい。</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>3</v>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MBGで「tolerates heat and humidity」と記載。北米東部原産のプレーリー植物で高温多湿耐性あり。</t>
+          <t>ヨーロッパ原産。高温・乾燥耐性あり。ただし高湿度・蒸れには弱く、水はけと通風確保が必要。</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3077,22 +2398,18 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>冷涼地原産。日本の高温多湿では夏越しが困難。梅雨〜夏は株が傷みやすい。高温多湿での葉枯れ・株腐れが発生しやすい。</t>
+          <t>地中海・中央アジア原産で乾燥を好む。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>3</v>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ヨーロッパ原産。高温・乾燥耐性あり。ただし高湿度・蒸れには弱く、水はけと通風確保が必要。</t>
+          <t>東アジア・日本原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3103,7 +2420,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>地中海・中央アジア原産で乾燥を好む。高湿度環境では根腐れしやすい。</t>
+          <t>東アジア原産。通風・水はけが良ければ夏越し可能。高湿度での灰色かびリスクあり。</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3114,7 +2431,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>東アジア・日本原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>通風・排水が良ければ夏越し可能。高湿度での根腐れリスクあり。種によって耐性が異なる。</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3125,7 +2442,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>東アジア原産。通風・水はけが良ければ夏越し可能。高湿度での灰色かびリスクあり。</t>
+          <t>中央アジア原産。高温・乾燥耐性あり。ただし高湿度・蒸れには弱く、水はけと通風確保が必要。</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3136,7 +2453,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>通風・排水が良ければ夏越し可能。高湿度での根腐れリスクあり。種によって耐性が異なる。</t>
+          <t>北米西部原産。通風・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3147,7 +2464,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>中央アジア原産。高温・乾燥耐性あり。ただし高湿度・蒸れには弱く、水はけと通風確保が必要。</t>
+          <t>ヨーロッパ原産。比較的高温多湿に適応するが、適湿管理が必要。</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3158,76 +2475,54 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>北米西部原産。通風・水はけが良ければ夏越し可能。</t>
+          <t>北米西部高山植物。高湿度環境では根腐れしやすい。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>3</v>
       </c>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ヨーロッパ原産。比較的高温多湿に適応するが、適湿管理が必要。</t>
+          <t>湿地・川辺原産で高湿度環境に適応。日本の梅雨〜夏の高湿度でも比較的安定。</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>3</v>
       </c>
-      <c r="C99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>北米西部高山植物。高湿度環境では根腐れしやすい。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>熱帯・亜熱帯原産のイネ科植物。高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>3</v>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>湿地・川辺原産で高湿度環境に適応。日本の梅雨〜夏の高湿度でも比較的安定。</t>
+          <t>北米東部原産。高温多湿に適応し、日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>3</v>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>熱帯・亜熱帯原産のイネ科植物。高温多湿耐性あり。日本でも夏越し安定。</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>3</v>
-      </c>
-      <c r="C102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>北米東部原産。高温多湿に適応し、日本でも夏越し安定。</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>3</v>
-      </c>
-      <c r="C103" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-validation/マスタ誤り疑いリスト.xlsx
+++ b/data-validation/マスタ誤り疑いリスト.xlsx
@@ -35,17 +35,12 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -75,12 +70,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -510,72 +504,72 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>カレックス‘バッドヘアーデイズ’</t>
+          <t>カレックス ディバルサ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Carex ‛Bad Hair Days’</t>
+          <t>Carex divulsa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>北米</t>
+          <t>ヨーロッパ、北アフリカ、コーカサス地域、中央アジア</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>耐潮性_根拠</t>
+          <t>耐暑性に関する注記</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>JSONの記述通りMangave属の園芸品種。多肉植物アガベの近縁であり、ナーサリーサイトで中程度の耐潮性があると記載。乾燥に強く排水を要す</t>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>耐潮性根拠に別分類群/多肉の記述が混入の疑い</t>
+          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>カレックス ディバルサ</t>
+          <t>カレックス フラジェリフェア ‘キウイ’</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Carex divulsa</t>
+          <t>Carex flagellifera 'Kiwi'</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ヨーロッパ、北アフリカ、コーカサス地域、中央アジア</t>
+          <t>ニュージーランド、タスマニア、チャタム諸島</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -594,33 +588,33 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>カレックス フラジェリフェア ‘キウイ’</t>
+          <t>ユーパトリウム　白花</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Carex flagellifera 'Kiwi'</t>
+          <t>Eupatorium album L.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ニュージーランド、タスマニア、チャタム諸島</t>
+          <t>北米東部</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of h</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -639,33 +633,33 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ユーパトリウム　白花</t>
+          <t>アルメリア　マリティマ ‘バリエガータ’（アルメリア斑入り）</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Eupatorium album L.</t>
+          <t>Armeria maritima 'Variegata'</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>北米東部</t>
+          <t>ヨーロッパ、北米</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -675,7 +669,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of h</t>
+          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -684,28 +678,28 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>アルメリア　マリティマ ‘バリエガータ’（アルメリア斑入り）</t>
+          <t>アルメリア　マリティマ ‘ルブリフォーリア’</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Armeria maritima 'Variegata'</t>
+          <t>Armeria maritima 'Rubrifolia'</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -733,29 +727,29 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>アルメリア　マリティマ ‘ルブリフォーリア’</t>
+          <t>アルメリア　マリティマ‘アルバ’ （アルメリア白花）</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Armeria maritima 'Rubrifolia'</t>
+          <t>Armeria maritima 'Alba'</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ヨーロッパ、北米</t>
+          <t>ヨーロッパ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -778,24 +772,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アルメリア　マリティマ‘アルバ’ （アルメリア白花）</t>
+          <t>アルメリア　マリティマ （アルメリア　ピンク）</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Armeria maritima 'Alba'</t>
+          <t>Armeria maritima</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -823,29 +817,29 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>アルメリア　マリティマ （アルメリア　ピンク）</t>
+          <t>ガリウム　ベラム（カワラマツバ）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Armeria maritima</t>
+          <t>Galium verum</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ヨーロッパ</t>
+          <t>ヨーロッパ、南西アジア</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -855,7 +849,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
+          <t>ヨーロッパ・アジアの森林下草。半日陰・湿潤環境を好む。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -864,33 +858,33 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ガリウム　ベラム（カワラマツバ）</t>
+          <t>ヤブラン白斑シルバードラゴン</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Galium verum</t>
+          <t>Liriope spicata 'Gin-ryū' (SILVER DRAGON)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ヨーロッパ、南西アジア</t>
+          <t>日本・中国</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,7 +894,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ヨーロッパ・アジアの森林下草。半日陰・湿潤環境を好む。通風確保で夏越し可能。</t>
+          <t>ヤブラン（Liriope muscari）：日本・東アジア原産の常緑多年草。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,33 +903,33 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ヤブラン白斑シルバードラゴン</t>
+          <t>ファラリス （フイリクサヨシ・アシフイリ）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Liriope spicata 'Gin-ryū' (SILVER DRAGON)</t>
+          <t>Phalaris arundinacea var. picta</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>日本・中国</t>
+          <t>ヨーロッパ・北アジア・北米</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -945,7 +939,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ヤブラン（Liriope muscari）：日本・東アジア原産の常緑多年草。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>ファラリス（Phalaris arundinacea）：湿地・川辺原産のイネ科植物。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -960,27 +954,27 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ファラリス （フイリクサヨシ・アシフイリ）</t>
+          <t>カレックス‘アイスファウンテン’</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phalaris arundinacea var. picta</t>
+          <t>Carex muskingumensis ‘Ice Fountains’</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ヨーロッパ・北アジア・北米</t>
+          <t>北米東部および中央部</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -990,187 +984,187 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ファラリス（Phalaris arundinacea）：湿地・川辺原産のイネ科植物。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
         </is>
       </c>
       <c r="I12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>カレックス　マスキングメンシス ‘リトルミッジ’</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Carex muskingumensis 'Little Midge'</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>北米東部</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>耐暑性に関する注記</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>トロリウス　チネンシス ‘ゴールデンクィーン’</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Trollius chinensis 'Golden Queen'</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>南シベリア、ロシア極東南部、中国北部</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>耐暑性に関する注記</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>フィソカルパス‘ディアボロ’ （アメリカテマリシモツケ ディアボロ）</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Physocarpus opulifolius ‛Diabolo’</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>北米東部</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>耐暑性に関する注記</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MBGで「hot, humid summers」には午後の日陰を推奨。Gardenia.netで「doesn't enjoy hot and</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>カレックス‘アイスファウンテン’</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Carex muskingumensis ‘Ice Fountains’</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>北米東部および中央部</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ユーパトリム　ルゴサム ‘チョコレート’</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ageratina altissima 'Chocolate'</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>北米東部</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>耐暑性に関する注記</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>カレックス　マスキングメンシス ‘リトルミッジ’</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Carex muskingumensis 'Little Midge'</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>トロリウス　チネンシス ‘ゴールデンクィーン’</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Trollius chinensis 'Golden Queen'</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>南シベリア、ロシア極東南部、中国北部</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>フィソカルパス‘ディアボロ’ （アメリカテマリシモツケ ディアボロ）</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Physocarpus opulifolius ‛Diabolo’</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MBGで「hot, humid summers」には午後の日陰を推奨。Gardenia.netで「doesn't enjoy hot and</t>
+          <t>北米東部原産。比較的高温多湿に適応するが、半日陰・適湿管理が必要。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1183,29 +1177,29 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>876</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ユーパトリム　ルゴサム ‘チョコレート’</t>
+          <t>ヤナギラン</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ageratina altissima 'Chocolate'</t>
+          <t>Chamerion angustifolium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>北米東部</t>
+          <t>北半球温帯全般 (ヨーロッパ、アジア、北アメリカ)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1215,7 +1209,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>北米東部原産。比較的高温多湿に適応するが、半日陰・適湿管理が必要。</t>
+          <t>北半球冷涼地原産。MBGで「Prefers part shade in hot summer climates」と明記。半日陰・適湿管理で夏</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1224,51 +1218,6 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ヤナギラン</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Chamerion angustifolium</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>北半球温帯全般 (ヨーロッパ、アジア、北アメリカ)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>北半球冷涼地原産。MBGで「Prefers part shade in hot summer climates」と明記。半日陰・適湿管理で夏</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1511,7 +1460,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/data-validation/マスタ誤り疑いリスト.xlsx
+++ b/data-validation/マスタ誤り疑いリスト.xlsx
@@ -35,22 +35,12 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -70,11 +60,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -499,726 +487,6 @@
         <is>
           <t>同一スタンプ波及行数</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>カレックス ディバルサ</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Carex divulsa</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、北アフリカ、コーカサス地域、中央アジア</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1892</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>カレックス フラジェリフェア ‘キウイ’</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Carex flagellifera 'Kiwi'</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ニュージーランド、タスマニア、チャタム諸島</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ユーパトリウム　白花</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Eupatorium album L.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of h</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ ‘バリエガータ’（アルメリア斑入り）</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Armeria maritima 'Variegata'</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、北米</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ ‘ルブリフォーリア’</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Armeria maritima 'Rubrifolia'</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、北米</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ‘アルバ’ （アルメリア白花）</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Armeria maritima 'Alba'</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ヨーロッパ</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>アルメリア　マリティマ （アルメリア　ピンク）</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Armeria maritima</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ヨーロッパ</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MBGで高温多湿・湿潤土壌での株腐れリスクを記載。地中海・ヨーロッパ沿岸原産で乾燥を好む。日本の梅雨〜夏は蒸れに弱い。</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1480</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ガリウム　ベラム（カワラマツバ）</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Galium verum</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ヨーロッパ、南西アジア</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ヨーロッパ・アジアの森林下草。半日陰・湿潤環境を好む。通風確保で夏越し可能。</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ヤブラン白斑シルバードラゴン</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Liriope spicata 'Gin-ryū' (SILVER DRAGON)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>日本・中国</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ヤブラン（Liriope muscari）：日本・東アジア原産の常緑多年草。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ファラリス （フイリクサヨシ・アシフイリ）</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Phalaris arundinacea var. picta</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ヨーロッパ・北アジア・北米</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ファラリス（Phalaris arundinacea）：湿地・川辺原産のイネ科植物。高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>注記は湿潤好きだが乾燥耐性(検証済)=強と矛盾</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>カレックス‘アイスファウンテン’</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Carex muskingumensis ‘Ice Fountains’</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>北米東部および中央部</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>817</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>カレックス　マスキングメンシス ‘リトルミッジ’</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Carex muskingumensis 'Little Midge'</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>トロリウス　チネンシス ‘ゴールデンクィーン’</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Trollius chinensis 'Golden Queen'</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>南シベリア、ロシア極東南部、中国北部</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>フィソカルパス‘ディアボロ’ （アメリカテマリシモツケ ディアボロ）</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Physocarpus opulifolius ‛Diabolo’</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MBGで「hot, humid summers」には午後の日陰を推奨。Gardenia.netで「doesn't enjoy hot and</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ユーパトリム　ルゴサム ‘チョコレート’</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Ageratina altissima 'Chocolate'</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>北米東部</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>北米東部原産。比較的高温多湿に適応するが、半日陰・適湿管理が必要。</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ヤナギラン</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Chamerion angustifolium</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>北半球温帯全般 (ヨーロッパ、アジア、北アメリカ)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>耐暑性に関する注記</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>北半球冷涼地原産。MBGで「Prefers part shade in hot summer climates」と明記。半日陰・適湿管理で夏</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>注記は日陰性だが日照条件=日向のみ（要確認）</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1456,22 +724,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
+          <t>地中海・ヨーロッパ原産。通風・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>11</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>地中海・ヨーロッパ原産。通風・水はけが良ければ夏越し可能。</t>
+          <t>北米西部原産。通風・水はけが良ければ夏越し可能。H. villosaは比較的蒸れ耐性あり。</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1482,7 +746,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>北米西部原産。通風・水はけが良ければ夏越し可能。H. villosaは比較的蒸れ耐性あり。</t>
+          <t>日本・東アジア原産。高温多湿に適応し、日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1493,44 +757,44 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>日本・東アジア原産。高温多湿に適応し、日本でも夏越し安定。</t>
+          <t>地中海原産で乾燥を好む。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>地中海原産で乾燥を好む。高湿度環境では根腐れしやすい。</t>
+          <t>ヨーロッパの森林下草。半日陰・湿潤環境を好む。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ヨーロッパの森林下草。半日陰・湿潤環境を好む。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
+          <t>ヨーロッパ・アジア原産。通風・水はけが良ければ夏越し可能。高湿度では根腐れリスクあり。</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ヨーロッパ・アジア原産。通風・水はけが良ければ夏越し可能。高湿度では根腐れリスクあり。</t>
+          <t>地中海・ヨーロッパ原産。高湿度環境では根腐れしやすい。</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1541,13 +805,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>地中海・ヨーロッパ原産。高湿度環境では根腐れしやすい。</t>
+          <t>湿地・森林下草で高湿度環境に適応。日本の梅雨〜夏の高湿度でも安定。</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1784,11 +1052,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of heat and humidity」と記載。北米湿地・草原原産で高温多湿耐性あり。</t>
+          <t>MBGで高温多湿環境での株腐れ（crown rot）リスクを記載。通風確保と水はけが必要。半日陰で管理すると夏越し安定。</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1799,22 +1067,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MBGで高温多湿環境での株腐れ（crown rot）リスクを記載。通風確保と水はけが必要。半日陰で管理すると夏越し安定。</t>
+          <t>東アジア原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>5</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>東アジア原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>日本・東アジア原産で高温多湿耐性あり。日本の夏越し安定。</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1825,7 +1089,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>日本・東アジア原産で高温多湿耐性あり。日本の夏越し安定。</t>
+          <t>MBGで「Tolerant of heat, humidity and drought」と記載。北米プレーリー原産で高温多湿耐性あり。日本でも夏越し安定。</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1836,7 +1100,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MBGで「Tolerant of heat, humidity and drought」と記載。北米プレーリー原産で高温多湿耐性あり。日本でも夏越し安定。</t>
+          <t>MBGで「better tolerance for heat in hot summers and for cold in cold winters than most other species of geranium」と記載。比較的蒸れ耐性あり。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1847,7 +1111,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MBGで「better tolerance for heat in hot summers and for cold in cold winters than most other species of geranium」と記載。比較的蒸れ耐性あり。通風確保で夏越し可能。</t>
+          <t>中南米山地原産。冷涼・湿潤環境を好む。日本の高温多湿では夏越しが困難。高温での株の傷みが発生しやすい。</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1858,33 +1122,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>中南米山地原産。冷涼・湿潤環境を好む。日本の高温多湿では夏越しが困難。高温での株の傷みが発生しやすい。</t>
+          <t>MBGで「tolerates full sun in cool summer climates」と記載。中央アジア・ヒマラヤ原産で高温多湿では半日陰が必要。水はけの良い土壌で夏越し可能。</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>5</v>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MBGで「tolerates full sun in cool summer climates」と記載。中央アジア・ヒマラヤ原産で高温多湿では半日陰が必要。水はけの良い土壌で夏越し可能。</t>
+          <t>MBGで「tolerates heat and humidity」と記載。北米・ヨーロッパ原産のイネ科植物で高温多湿耐性あり。</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>5</v>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MBGで「tolerates heat and humidity」と記載。北米・ヨーロッパ原産のイネ科植物で高温多湿耐性あり。</t>
+          <t>ヨーロッパ原産のイネ科植物。通風・水はけが良ければ夏越し可能。</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1895,7 +1159,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ヨーロッパ原産のイネ科植物。通風・水はけが良ければ夏越し可能。</t>
+          <t>日本・東アジア原産のイネ科植物。MBGで「Tolerant of summer heat and humidity」と記載。日本の高温多湿環境に適応。夏越し安定。</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1906,18 +1170,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>日本・東アジア原産のイネ科植物。MBGで「Tolerant of summer heat and humidity」と記載。日本の高温多湿環境に適応。夏越し安定。</t>
+          <t>冷涼地原産のイネ科植物。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>5</v>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>冷涼地原産のイネ科植物。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
+          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1932,7 +1200,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>冷涼地・湿地原産。日本の高温多湿では半日陰管理が必要。通風確保で夏越し可能。</t>
+          <t>MBGで湿潤環境を好むと記載。Plant Delightsで「still in full flower after a month of heat and humidity」と記載。北米湿地・草原原産で高温多湿耐性あり。</t>
         </is>
       </c>
       <c r="B58" t="n">

--- a/data-validation/マスタ誤り疑いリスト.xlsx
+++ b/data-validation/マスタ誤り疑いリスト.xlsx
@@ -35,12 +35,17 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,9 +65,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -487,6 +493,906 @@
         <is>
           <t>同一スタンプ波及行数</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>オレガノ　ブルガレ‘オーレウム’ （ゴールデンオレガノ）</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Origanum vulgare 'Aureum'</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ヨーロッパ、地中海沿岸、西アジア</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>オレガノ　ブルガレ‘ジムベスト’</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Origanum vulgare 'Jim Best'</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ヨーロッパ、地中海沿岸、西アジア</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>アルケミラ　サクサティリス</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Alchemilla saxatilis</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>高ピレネー山脈、スペインからオーストリア、イタリア</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>株立ち</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ゲラニウム　ヒマライエンス</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Geranium himalayense</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ヒマラヤ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ゲラニウム　マクロリズム ‘ビーバンズバラエティ'(ｾﾞﾗﾆｳﾑﾙｰﾄ)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Geranium macrorrhizum 'Bevan's Variety'</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>南東ヨーロッパ、バルカン半島</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ゲンチアナ　クルシアータ ‘ブルークロス’</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Gentiana cruciata 'Blue Cross'</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ヨーロッパ、西アジア、ユーラシア高山帯</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>アスチルベ　アレンジー‘ショースター’</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Astilbe × arendsii 'Showstar'</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>東アジア、北米東部</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1156</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ゲラニウム‘ブルーサンライズ’</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Geranium ‛Blue Sunrise’</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>オランダ (園芸品種)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ゲラニウム　マクロリズム ‘アルバム’（ゼラニウムルート)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Geranium macrorrhizum 'Album'</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>南東アルプス、バルカン半島</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ヘメロカリス‘ビッグタイムハピー’</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hemerocallis 'Big Time Happy'</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>東アジア、ヨーロッパ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>株立ち</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>フロックス　パニキュラータ‘ローラ’</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Phlox paniculata 'Laura'</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>米国東部および中央部</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>株立ち</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>サンギソルバ　オフィシナリス　 var.マイクロセファラ（ﾋﾒﾜﾚﾓｺｳ）</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sanguisorba officinalis var. microcephala</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>北半球の冷涼地域（ヨーロッパ、北アジア、北米西部）</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>カレックス‘バーグレニーアイ’</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Carex talbotii</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ニュージーランド</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>グラス</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=グラス（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ゲラニウム　オクソニアナム ‘ワーグレーブピンク’</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Geranium × oxonianum 'Wargrave Pink'</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ヨーロッパ (園芸品種)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>アキレア　ミレフォリウム ‘レッドベルベット’</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Achillea millefolium 'Red Velvet'</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ヨーロッパ、アジア、北米</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ペンステモン　ハシュータス  var.ピグマエウス f.　アルバス</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Penstemon hirsutus var. pygmaeus f. albus</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>北米東部</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ゲラニウム‘アズールラッシュ’</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Geranium 'Azure Rush'</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ドイツ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ゲラニウム　マクロリズム ‘スペサート’（ゼラニウムルート）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Geranium macrorrhizum 'Spessart'</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>南ヨーロッパ、トルコ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1822</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ゲラニウム　エンドレッシー</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Geranium endressii</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ピレネー山脈（スペイン、フランス）</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ドーム</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ゲラニウム‘フェイアンナ’</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Geranium wlassovianum 'Fay Anna'</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>シベリア、モンゴル、東ロシア、中国北部</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>成株シルエット</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>株立ち</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data-validation/マスタ誤り疑いリスト.xlsx
+++ b/data-validation/マスタ誤り疑いリスト.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>499</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>アルケミラ　サクサティリス</t>
+          <t>ゲラニウム　ヒマライエンス</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alchemilla saxatilis</t>
+          <t>Geranium himalayense</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>高ピレネー山脈、スペインからオーストリア、イタリア</t>
+          <t>ヒマラヤ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -618,12 +618,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>株立ち</t>
+          <t>ドーム</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -638,22 +638,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>578</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ゲラニウム　ヒマライエンス</t>
+          <t>ゲラニウム　マクロリズム ‘ビーバンズバラエティ'(ｾﾞﾗﾆｳﾑﾙｰﾄ)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Geranium himalayense</t>
+          <t>Geranium macrorrhizum 'Bevan's Variety'</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ヒマラヤ</t>
+          <t>南東ヨーロッパ、バルカン半島</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -683,22 +683,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>986</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ゲラニウム　マクロリズム ‘ビーバンズバラエティ'(ｾﾞﾗﾆｳﾑﾙｰﾄ)</t>
+          <t>ゲンチアナ　クルシアータ ‘ブルークロス’</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Geranium macrorrhizum 'Bevan's Variety'</t>
+          <t>Gentiana cruciata 'Blue Cross'</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>南東ヨーロッパ、バルカン半島</t>
+          <t>ヨーロッパ、西アジア、ユーラシア高山帯</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -728,22 +728,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ゲンチアナ　クルシアータ ‘ブルークロス’</t>
+          <t>アスチルベ　アレンジー‘ショースター’</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gentiana cruciata 'Blue Cross'</t>
+          <t>Astilbe × arendsii 'Showstar'</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ヨーロッパ、西アジア、ユーラシア高山帯</t>
+          <t>東アジア、北米東部</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -773,22 +773,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>アスチルベ　アレンジー‘ショースター’</t>
+          <t>ゲラニウム‘ブルーサンライズ’</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Astilbe × arendsii 'Showstar'</t>
+          <t>Geranium ‛Blue Sunrise’</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>東アジア、北米東部</t>
+          <t>オランダ (園芸品種)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -818,22 +818,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ゲラニウム‘ブルーサンライズ’</t>
+          <t>ゲラニウム　マクロリズム ‘アルバム’（ゼラニウムルート)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Geranium ‛Blue Sunrise’</t>
+          <t>Geranium macrorrhizum 'Album'</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>オランダ (園芸品種)</t>
+          <t>南東アルプス、バルカン半島</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -863,22 +863,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ゲラニウム　マクロリズム ‘アルバム’（ゼラニウムルート)</t>
+          <t>ヘメロカリス‘ビッグタイムハピー’</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Geranium macrorrhizum 'Album'</t>
+          <t>Hemerocallis 'Big Time Happy'</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>南東アルプス、バルカン半島</t>
+          <t>東アジア、ヨーロッパ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ドーム</t>
+          <t>株立ち</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -908,22 +908,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ヘメロカリス‘ビッグタイムハピー’</t>
+          <t>フロックス　パニキュラータ‘ローラ’</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hemerocallis 'Big Time Happy'</t>
+          <t>Phlox paniculata 'Laura'</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>東アジア、ヨーロッパ</t>
+          <t>米国東部および中央部</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>フロックス　パニキュラータ‘ローラ’</t>
+          <t>サンギソルバ　オフィシナリス　 var.マイクロセファラ（ﾋﾒﾜﾚﾓｺｳ）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phlox paniculata 'Laura'</t>
+          <t>Sanguisorba officinalis var. microcephala</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>米国東部および中央部</t>
+          <t>北半球の冷涼地域（ヨーロッパ、北アジア、北米西部）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>株立ち</t>
+          <t>ドーム</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -998,22 +998,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>サンギソルバ　オフィシナリス　 var.マイクロセファラ（ﾋﾒﾜﾚﾓｺｳ）</t>
+          <t>ゲラニウム　オクソニアナム ‘ワーグレーブピンク’</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sanguisorba officinalis var. microcephala</t>
+          <t>Geranium × oxonianum 'Wargrave Pink'</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>北半球の冷涼地域（ヨーロッパ、北アジア、北米西部）</t>
+          <t>ヨーロッパ (園芸品種)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1043,22 +1043,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>カレックス‘バーグレニーアイ’</t>
+          <t>アキレア　ミレフォリウム ‘レッドベルベット’</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Carex talbotii</t>
+          <t>Achillea millefolium 'Red Velvet'</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ニュージーランド</t>
+          <t>ヨーロッパ、アジア、北米</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>グラス</t>
+          <t>ドーム</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=グラス（形状分類の要確認）</t>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1088,22 +1088,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ゲラニウム　オクソニアナム ‘ワーグレーブピンク’</t>
+          <t>ペンステモン　ハシュータス  var.ピグマエウス f.　アルバス</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Geranium × oxonianum 'Wargrave Pink'</t>
+          <t>Penstemon hirsutus var. pygmaeus f. albus</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ヨーロッパ (園芸品種)</t>
+          <t>北米東部</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1133,22 +1133,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>アキレア　ミレフォリウム ‘レッドベルベット’</t>
+          <t>ゲラニウム‘アズールラッシュ’</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Achillea millefolium 'Red Velvet'</t>
+          <t>Geranium 'Azure Rush'</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ヨーロッパ、アジア、北米</t>
+          <t>ドイツ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1178,22 +1178,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1555</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ペンステモン　ハシュータス  var.ピグマエウス f.　アルバス</t>
+          <t>ゲラニウム　マクロリズム ‘スペサート’（ゼラニウムルート）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Penstemon hirsutus var. pygmaeus f. albus</t>
+          <t>Geranium macrorrhizum 'Spessart'</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>北米東部</t>
+          <t>南ヨーロッパ、トルコ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1223,22 +1223,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ゲラニウム‘アズールラッシュ’</t>
+          <t>ゲラニウム　エンドレッシー</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Geranium 'Azure Rush'</t>
+          <t>Geranium endressii</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ドイツ</t>
+          <t>ピレネー山脈（スペイン、フランス）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1268,22 +1268,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ゲラニウム　マクロリズム ‘スペサート’（ゼラニウムルート）</t>
+          <t>ゲラニウム‘フェイアンナ’</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Geranium macrorrhizum 'Spessart'</t>
+          <t>Geranium wlassovianum 'Fay Anna'</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>南ヨーロッパ、トルコ</t>
+          <t>シベリア、モンゴル、東ロシア、中国北部</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1293,105 +1293,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ドーム</t>
+          <t>株立ち</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
+          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1822</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ゲラニウム　エンドレッシー</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Geranium endressii</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ピレネー山脈（スペイン、フランス）</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>成株シルエット</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ドーム</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=ドーム（形状分類の要確認）</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ゲラニウム‘フェイアンナ’</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Geranium wlassovianum 'Fay Anna'</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>シベリア、モンゴル、東ロシア、中国北部</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>成株シルエット</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>株立ち</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>シルエット理由はマット状/GC(H&lt;W)だが値=株立ち（形状分類の要確認）</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
         <v>1</v>
       </c>
     </row>
